--- a/Team-Data/2012-13/12-11-2012-13.xlsx
+++ b/Team-Data/2012-13/12-11-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -760,7 +827,7 @@
         <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL2" t="n">
         <v>5</v>
@@ -775,7 +842,7 @@
         <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ2" t="n">
         <v>28</v>
@@ -787,7 +854,7 @@
         <v>25</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
         <v>4</v>
@@ -814,7 +881,7 @@
         <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
         <v>11</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
         <v>6</v>
@@ -951,7 +1018,7 @@
         <v>29</v>
       </c>
       <c r="AN3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
         <v>11</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -984,7 +1051,7 @@
         <v>27</v>
       </c>
       <c r="AY3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ3" t="n">
         <v>21</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
         <v>11</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>0.55</v>
+        <v>0.579</v>
       </c>
       <c r="H4" t="n">
         <v>48.3</v>
@@ -1043,67 +1110,67 @@
         <v>35.8</v>
       </c>
       <c r="J4" t="n">
-        <v>80.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.443</v>
+        <v>0.439</v>
       </c>
       <c r="L4" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M4" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="O4" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="P4" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.728</v>
+        <v>0.727</v>
       </c>
       <c r="R4" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="S4" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T4" t="n">
-        <v>42</v>
+        <v>42.3</v>
       </c>
       <c r="U4" t="n">
         <v>21.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W4" t="n">
         <v>6.9</v>
       </c>
       <c r="X4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="AA4" t="n">
         <v>21.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.2</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE4" t="n">
         <v>11</v>
@@ -1112,37 +1179,37 @@
         <v>9</v>
       </c>
       <c r="AG4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI4" t="n">
         <v>21</v>
       </c>
       <c r="AJ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AL4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AN4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AO4" t="n">
         <v>17</v>
       </c>
       <c r="AP4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR4" t="n">
         <v>6</v>
@@ -1151,28 +1218,28 @@
         <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU4" t="n">
         <v>15</v>
       </c>
       <c r="AV4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY4" t="n">
         <v>4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB4" t="n">
         <v>19</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG5" t="n">
         <v>23</v>
@@ -1303,7 +1370,7 @@
         <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
@@ -1315,7 +1382,7 @@
         <v>17</v>
       </c>
       <c r="AN5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
         <v>4</v>
@@ -1336,13 +1403,13 @@
         <v>17</v>
       </c>
       <c r="AU5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV5" t="n">
         <v>8</v>
       </c>
       <c r="AW5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX5" t="n">
         <v>4</v>
@@ -1354,13 +1421,13 @@
         <v>10</v>
       </c>
       <c r="BA5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB5" t="n">
         <v>18</v>
       </c>
       <c r="BC5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
         <v>11</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.55</v>
+        <v>0.579</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
@@ -1407,49 +1474,49 @@
         <v>35.6</v>
       </c>
       <c r="J6" t="n">
-        <v>80.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.442</v>
+        <v>0.444</v>
       </c>
       <c r="L6" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="M6" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="N6" t="n">
-        <v>0.345</v>
+        <v>0.332</v>
       </c>
       <c r="O6" t="n">
-        <v>18.4</v>
+        <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.801</v>
+        <v>0.803</v>
       </c>
       <c r="R6" t="n">
-        <v>12.8</v>
+        <v>12.5</v>
       </c>
       <c r="S6" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T6" t="n">
-        <v>44.5</v>
+        <v>44.2</v>
       </c>
       <c r="U6" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="V6" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W6" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
         <v>5.5</v>
@@ -1458,16 +1525,16 @@
         <v>19.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.7</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>93.90000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
         <v>11</v>
@@ -1476,10 +1543,10 @@
         <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
         <v>22</v>
@@ -1488,7 +1555,7 @@
         <v>23</v>
       </c>
       <c r="AK6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1497,19 +1564,19 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
         <v>2</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
         <v>9</v>
@@ -1518,16 +1585,16 @@
         <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW6" t="n">
         <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY6" t="n">
         <v>18</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -1571,97 +1638,97 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>0.227</v>
+        <v>0.19</v>
       </c>
       <c r="H7" t="n">
         <v>48.5</v>
       </c>
       <c r="I7" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J7" t="n">
-        <v>85.59999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0.413</v>
+        <v>0.412</v>
       </c>
       <c r="L7" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M7" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0.346</v>
+        <v>0.342</v>
       </c>
       <c r="O7" t="n">
         <v>15.9</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.721</v>
+        <v>0.729</v>
       </c>
       <c r="R7" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="S7" t="n">
-        <v>28.6</v>
+        <v>28.3</v>
       </c>
       <c r="T7" t="n">
         <v>42.7</v>
       </c>
       <c r="U7" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="V7" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W7" t="n">
         <v>8.5</v>
       </c>
       <c r="X7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>94.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>-5.6</v>
+        <v>-6.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG7" t="n">
         <v>28</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
         <v>23</v>
@@ -1673,13 +1740,13 @@
         <v>29</v>
       </c>
       <c r="AL7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM7" t="n">
         <v>7</v>
       </c>
-      <c r="AM7" t="n">
-        <v>4</v>
-      </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>22</v>
@@ -1688,19 +1755,19 @@
         <v>20</v>
       </c>
       <c r="AQ7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR7" t="n">
         <v>2</v>
       </c>
       <c r="AS7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AV7" t="n">
         <v>26</v>
@@ -1715,13 +1782,13 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="BA7" t="n">
         <v>15</v>
       </c>
       <c r="BB7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC7" t="n">
         <v>26</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1855,13 +1922,13 @@
         <v>10</v>
       </c>
       <c r="AL8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
         <v>15</v>
@@ -1879,16 +1946,16 @@
         <v>8</v>
       </c>
       <c r="AT8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU8" t="n">
         <v>14</v>
       </c>
       <c r="AV8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -1897,7 +1964,7 @@
         <v>6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA8" t="n">
         <v>17</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -1935,25 +2002,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F9" t="n">
         <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.476</v>
       </c>
       <c r="H9" t="n">
         <v>48.5</v>
       </c>
       <c r="I9" t="n">
-        <v>38.8</v>
+        <v>38.9</v>
       </c>
       <c r="J9" t="n">
-        <v>84.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K9" t="n">
         <v>0.461</v>
@@ -1962,73 +2029,73 @@
         <v>6.1</v>
       </c>
       <c r="M9" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.328</v>
+        <v>0.327</v>
       </c>
       <c r="O9" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="P9" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.676</v>
+        <v>0.68</v>
       </c>
       <c r="R9" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="S9" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T9" t="n">
-        <v>45.2</v>
+        <v>45.6</v>
       </c>
       <c r="U9" t="n">
         <v>22</v>
       </c>
       <c r="V9" t="n">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="W9" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X9" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="AB9" t="n">
         <v>100.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AF9" t="n">
         <v>17</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ9" t="n">
         <v>5</v>
@@ -2058,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
         <v>6</v>
@@ -2082,7 +2149,7 @@
         <v>13</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BB9" t="n">
         <v>9</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
         <v>7</v>
       </c>
       <c r="F10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G10" t="n">
-        <v>0.292</v>
+        <v>0.304</v>
       </c>
       <c r="H10" t="n">
         <v>48</v>
@@ -2135,64 +2202,64 @@
         <v>35</v>
       </c>
       <c r="J10" t="n">
-        <v>79.2</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L10" t="n">
         <v>5.8</v>
       </c>
       <c r="M10" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.371</v>
+        <v>0.37</v>
       </c>
       <c r="O10" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P10" t="n">
-        <v>25.4</v>
+        <v>25.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.732</v>
+        <v>0.735</v>
       </c>
       <c r="R10" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="T10" t="n">
-        <v>41.4</v>
+        <v>41</v>
       </c>
       <c r="U10" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V10" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W10" t="n">
         <v>6.3</v>
       </c>
       <c r="X10" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="Z10" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB10" t="n">
         <v>94.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3</v>
+        <v>-2.8</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -2213,55 +2280,55 @@
         <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL10" t="n">
         <v>24</v>
       </c>
       <c r="AM10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN10" t="n">
         <v>10</v>
       </c>
       <c r="AO10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV10" t="n">
         <v>16</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>18</v>
       </c>
       <c r="AW10" t="n">
         <v>27</v>
       </c>
       <c r="AX10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA10" t="n">
         <v>7</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -2377,10 +2444,10 @@
         <v>0.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
@@ -2404,7 +2471,7 @@
         <v>14</v>
       </c>
       <c r="AM11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN11" t="n">
         <v>13</v>
@@ -2419,22 +2486,22 @@
         <v>11</v>
       </c>
       <c r="AR11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS11" t="n">
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
       </c>
       <c r="AV11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX11" t="n">
         <v>29</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-0.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
         <v>18</v>
@@ -2628,7 +2695,7 @@
         <v>12</v>
       </c>
       <c r="BA12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB12" t="n">
         <v>3</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>-1</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF13" t="n">
         <v>17</v>
       </c>
       <c r="AG13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH13" t="n">
         <v>8</v>
@@ -2759,7 +2826,7 @@
         <v>30</v>
       </c>
       <c r="AJ13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK13" t="n">
         <v>28</v>
@@ -2768,22 +2835,22 @@
         <v>18</v>
       </c>
       <c r="AM13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN13" t="n">
         <v>24</v>
       </c>
       <c r="AO13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP13" t="n">
         <v>18</v>
       </c>
       <c r="AQ13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS13" t="n">
         <v>2</v>
@@ -2792,13 +2859,13 @@
         <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV13" t="n">
         <v>20</v>
       </c>
       <c r="AW13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX13" t="n">
         <v>3</v>
@@ -2813,7 +2880,7 @@
         <v>14</v>
       </c>
       <c r="BB13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -2845,58 +2912,58 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.714</v>
+        <v>0.7</v>
       </c>
       <c r="H14" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I14" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J14" t="n">
-        <v>80.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="K14" t="n">
         <v>0.48</v>
       </c>
       <c r="L14" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>19.4</v>
+        <v>19.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O14" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P14" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.739</v>
+        <v>0.741</v>
       </c>
       <c r="R14" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S14" t="n">
         <v>29.6</v>
       </c>
       <c r="T14" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U14" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="V14" t="n">
         <v>14.9</v>
@@ -2905,25 +2972,25 @@
         <v>11</v>
       </c>
       <c r="X14" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>101.9</v>
+        <v>102.3</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
@@ -2935,7 +3002,7 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2947,10 +3014,10 @@
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AN14" t="n">
         <v>16</v>
@@ -2959,7 +3026,7 @@
         <v>12</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ14" t="n">
         <v>22</v>
@@ -2968,16 +3035,16 @@
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT14" t="n">
         <v>23</v>
       </c>
       <c r="AU14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>1</v>
@@ -2989,10 +3056,10 @@
         <v>7</v>
       </c>
       <c r="AZ14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -3027,106 +3094,106 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
         <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" t="n">
-        <v>0.409</v>
+        <v>0.429</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>35.9</v>
+        <v>36.1</v>
       </c>
       <c r="J15" t="n">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.455</v>
+        <v>0.457</v>
       </c>
       <c r="L15" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="M15" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.381</v>
+        <v>0.388</v>
       </c>
       <c r="O15" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="P15" t="n">
-        <v>30.8</v>
+        <v>30.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.675</v>
+        <v>0.678</v>
       </c>
       <c r="R15" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S15" t="n">
-        <v>33.1</v>
+        <v>32.8</v>
       </c>
       <c r="T15" t="n">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="V15" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="W15" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="X15" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA15" t="n">
         <v>24.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.5</v>
+        <v>101.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>18</v>
       </c>
       <c r="AF15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH15" t="n">
         <v>28</v>
       </c>
       <c r="AI15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL15" t="n">
         <v>3</v>
@@ -3135,7 +3202,7 @@
         <v>3</v>
       </c>
       <c r="AN15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO15" t="n">
         <v>2</v>
@@ -3147,7 +3214,7 @@
         <v>30</v>
       </c>
       <c r="AR15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS15" t="n">
         <v>4</v>
@@ -3156,22 +3223,22 @@
         <v>2</v>
       </c>
       <c r="AU15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV15" t="n">
         <v>29</v>
       </c>
       <c r="AW15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX15" t="n">
         <v>10</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3180,7 +3247,7 @@
         <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -3290,7 +3357,7 @@
         <v>27</v>
       </c>
       <c r="AE16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF16" t="n">
         <v>1</v>
@@ -3308,13 +3375,13 @@
         <v>17</v>
       </c>
       <c r="AK16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL16" t="n">
         <v>26</v>
       </c>
       <c r="AM16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN16" t="n">
         <v>11</v>
@@ -3323,22 +3390,22 @@
         <v>7</v>
       </c>
       <c r="AP16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
         <v>3</v>
       </c>
       <c r="AR16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV16" t="n">
         <v>13</v>
@@ -3350,13 +3417,13 @@
         <v>12</v>
       </c>
       <c r="AY16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
         <v>20</v>
       </c>
       <c r="BA16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB16" t="n">
         <v>12</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>4.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF17" t="n">
         <v>4</v>
@@ -3484,7 +3551,7 @@
         <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ17" t="n">
         <v>28</v>
@@ -3523,7 +3590,7 @@
         <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW17" t="n">
         <v>17</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-0.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
         <v>14</v>
@@ -3696,7 +3763,7 @@
         <v>15</v>
       </c>
       <c r="AS18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT18" t="n">
         <v>16</v>
@@ -3705,7 +3772,7 @@
         <v>6</v>
       </c>
       <c r="AV18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW18" t="n">
         <v>6</v>
@@ -3720,7 +3787,7 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB18" t="n">
         <v>17</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3906,7 @@
         <v>18</v>
       </c>
       <c r="AF19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG19" t="n">
         <v>16</v>
@@ -3875,7 +3942,7 @@
         <v>27</v>
       </c>
       <c r="AR19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
         <v>6</v>
@@ -3884,22 +3951,22 @@
         <v>3</v>
       </c>
       <c r="AU19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY19" t="n">
         <v>20</v>
       </c>
-      <c r="AV19" t="n">
-        <v>23</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>19</v>
-      </c>
       <c r="AZ19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -3937,85 +4004,85 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" t="n">
         <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>0.25</v>
+        <v>0.263</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>34.6</v>
+        <v>35</v>
       </c>
       <c r="J20" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.438</v>
+        <v>0.445</v>
       </c>
       <c r="L20" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="M20" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0.389</v>
+        <v>0.395</v>
       </c>
       <c r="O20" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="P20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.789</v>
+      </c>
+      <c r="R20" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="S20" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>6</v>
+      </c>
+      <c r="X20" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="AA20" t="n">
         <v>19.6</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0.781</v>
-      </c>
-      <c r="R20" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="S20" t="n">
-        <v>29.9</v>
-      </c>
-      <c r="T20" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="U20" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="V20" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="W20" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="X20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>19.7</v>
-      </c>
       <c r="AB20" t="n">
-        <v>91.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>-6.4</v>
+        <v>-6.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>27</v>
@@ -4030,64 +4097,64 @@
         <v>13</v>
       </c>
       <c r="AI20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ20" t="n">
         <v>27</v>
       </c>
       <c r="AK20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM20" t="n">
         <v>20</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>22</v>
       </c>
       <c r="AN20" t="n">
         <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR20" t="n">
         <v>22</v>
       </c>
       <c r="AS20" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AU20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AV20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BB20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -4119,55 +4186,55 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
         <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>0.762</v>
+        <v>0.75</v>
       </c>
       <c r="H21" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="J21" t="n">
-        <v>83.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K21" t="n">
         <v>0.447</v>
       </c>
       <c r="L21" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="M21" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.409</v>
+        <v>0.405</v>
       </c>
       <c r="O21" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="P21" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R21" t="n">
         <v>10.4</v>
       </c>
       <c r="S21" t="n">
-        <v>29.3</v>
+        <v>29.5</v>
       </c>
       <c r="T21" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="U21" t="n">
         <v>20</v>
@@ -4176,28 +4243,28 @@
         <v>10.9</v>
       </c>
       <c r="W21" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="X21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA21" t="n">
         <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>102.6</v>
+        <v>102.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>3</v>
@@ -4209,16 +4276,16 @@
         <v>4</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI21" t="n">
         <v>13</v>
       </c>
       <c r="AJ21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AK21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL21" t="n">
         <v>1</v>
@@ -4230,7 +4297,7 @@
         <v>3</v>
       </c>
       <c r="AO21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP21" t="n">
         <v>21</v>
@@ -4239,13 +4306,13 @@
         <v>14</v>
       </c>
       <c r="AR21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AT21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU21" t="n">
         <v>25</v>
@@ -4257,7 +4324,7 @@
         <v>4</v>
       </c>
       <c r="AX21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY21" t="n">
         <v>5</v>
@@ -4266,7 +4333,7 @@
         <v>3</v>
       </c>
       <c r="BA21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB21" t="n">
         <v>5</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4403,10 +4470,10 @@
         <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN22" t="n">
         <v>2</v>
@@ -4427,13 +4494,13 @@
         <v>7</v>
       </c>
       <c r="AT22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU22" t="n">
         <v>11</v>
       </c>
       <c r="AV22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW22" t="n">
         <v>22</v>
@@ -4448,7 +4515,7 @@
         <v>19</v>
       </c>
       <c r="BA22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-3.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
         <v>22</v>
@@ -4573,7 +4640,7 @@
         <v>22</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>15</v>
@@ -4582,7 +4649,7 @@
         <v>13</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
         <v>28</v>
@@ -4627,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -4743,22 +4810,22 @@
         <v>-1.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>8</v>
       </c>
       <c r="AF24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AH24" t="n">
         <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ24" t="n">
         <v>8</v>
@@ -4779,7 +4846,7 @@
         <v>28</v>
       </c>
       <c r="AP24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ24" t="n">
         <v>21</v>
@@ -4791,19 +4858,19 @@
         <v>16</v>
       </c>
       <c r="AT24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
       </c>
       <c r="AW24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX24" t="n">
         <v>13</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>14</v>
       </c>
       <c r="AY24" t="n">
         <v>13</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4998,7 @@
         <v>23</v>
       </c>
       <c r="AF25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG25" t="n">
         <v>25</v>
@@ -4946,7 +5013,7 @@
         <v>4</v>
       </c>
       <c r="AK25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL25" t="n">
         <v>22</v>
@@ -4955,10 +5022,10 @@
         <v>19</v>
       </c>
       <c r="AN25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP25" t="n">
         <v>25</v>
@@ -4967,22 +5034,22 @@
         <v>18</v>
       </c>
       <c r="AR25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS25" t="n">
         <v>28</v>
       </c>
       <c r="AT25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV25" t="n">
         <v>7</v>
       </c>
       <c r="AW25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX25" t="n">
         <v>9</v>
@@ -4994,7 +5061,7 @@
         <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5122,7 +5189,7 @@
         <v>1</v>
       </c>
       <c r="AI26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
         <v>15</v>
@@ -5131,13 +5198,13 @@
         <v>23</v>
       </c>
       <c r="AL26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM26" t="n">
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO26" t="n">
         <v>16</v>
@@ -5152,10 +5219,10 @@
         <v>11</v>
       </c>
       <c r="AS26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU26" t="n">
         <v>29</v>
@@ -5164,7 +5231,7 @@
         <v>16</v>
       </c>
       <c r="AW26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX26" t="n">
         <v>20</v>
@@ -5173,7 +5240,7 @@
         <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
         <v>17</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -5289,19 +5356,19 @@
         <v>-5</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>23</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AI27" t="n">
         <v>17</v>
@@ -5316,7 +5383,7 @@
         <v>21</v>
       </c>
       <c r="AM27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AN27" t="n">
         <v>15</v>
@@ -5334,10 +5401,10 @@
         <v>18</v>
       </c>
       <c r="AS27" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5346,7 +5413,7 @@
         <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX27" t="n">
         <v>25</v>
@@ -5355,13 +5422,13 @@
         <v>26</v>
       </c>
       <c r="AZ27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA27" t="n">
         <v>28</v>
       </c>
       <c r="BB27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK28" t="n">
         <v>3</v>
@@ -5528,10 +5595,10 @@
         <v>22</v>
       </c>
       <c r="AW28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY28" t="n">
         <v>17</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5723,7 @@
         <v>2</v>
       </c>
       <c r="AE29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF29" t="n">
         <v>30</v>
@@ -5665,19 +5732,19 @@
         <v>29</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
         <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK29" t="n">
         <v>26</v>
       </c>
       <c r="AL29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
@@ -5689,16 +5756,16 @@
         <v>10</v>
       </c>
       <c r="AP29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR29" t="n">
         <v>21</v>
       </c>
       <c r="AS29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT29" t="n">
         <v>22</v>
@@ -5713,7 +5780,7 @@
         <v>26</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
         <v>24</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -5853,16 +5920,16 @@
         <v>8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK30" t="n">
         <v>11</v>
       </c>
       <c r="AL30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN30" t="n">
         <v>8</v>
@@ -5871,7 +5938,7 @@
         <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ30" t="n">
         <v>12</v>
@@ -5880,7 +5947,7 @@
         <v>3</v>
       </c>
       <c r="AS30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT30" t="n">
         <v>8</v>
@@ -5889,10 +5956,10 @@
         <v>5</v>
       </c>
       <c r="AV30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW30" t="n">
         <v>11</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>10</v>
       </c>
       <c r="AX30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
@@ -5939,103 +6006,103 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
         <v>15</v>
       </c>
       <c r="G31" t="n">
-        <v>0.167</v>
+        <v>0.118</v>
       </c>
       <c r="H31" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="I31" t="n">
-        <v>34.1</v>
+        <v>34.5</v>
       </c>
       <c r="J31" t="n">
-        <v>83.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.407</v>
+        <v>0.412</v>
       </c>
       <c r="L31" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M31" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.313</v>
+        <v>0.315</v>
       </c>
       <c r="O31" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="P31" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="R31" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="S31" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="U31" t="n">
         <v>20.8</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="R31" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="S31" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="U31" t="n">
-        <v>20.4</v>
       </c>
       <c r="V31" t="n">
         <v>15.2</v>
       </c>
       <c r="W31" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="X31" t="n">
         <v>4.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.7</v>
+        <v>19.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>90.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6.6</v>
+        <v>-7.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
         <v>30</v>
       </c>
       <c r="AH31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI31" t="n">
         <v>28</v>
       </c>
       <c r="AJ31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
@@ -6050,7 +6117,7 @@
         <v>29</v>
       </c>
       <c r="AO31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP31" t="n">
         <v>24</v>
@@ -6059,40 +6126,40 @@
         <v>20</v>
       </c>
       <c r="AR31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT31" t="n">
         <v>14</v>
       </c>
-      <c r="AT31" t="n">
-        <v>12</v>
-      </c>
       <c r="AU31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV31" t="n">
         <v>19</v>
       </c>
       <c r="AW31" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
         <v>21</v>
       </c>
       <c r="AY31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
         <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BB31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-11-2012-13</t>
+          <t>2012-12-11</t>
         </is>
       </c>
     </row>
